--- a/data/trans_dic/P43B-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P43B-Provincia-trans_dic.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,14%</t>
         </is>
       </c>
     </row>
@@ -635,32 +635,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,0; 16,51</t>
+          <t>5,8; 16,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,02; 24,87</t>
+          <t>11,97; 25,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,42; 21,92</t>
+          <t>10,97; 21,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,0; 16,51</t>
+          <t>5,8; 16,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,02; 24,87</t>
+          <t>11,97; 25,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,42; 21,92</t>
+          <t>10,97; 21,37</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,48%</t>
         </is>
       </c>
     </row>
@@ -715,32 +715,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,93; 19,58</t>
+          <t>9,09; 19,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,88; 11,8</t>
+          <t>4,68; 11,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,16; 18,75</t>
+          <t>10,89; 18,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,93; 19,58</t>
+          <t>9,09; 19,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,88; 11,8</t>
+          <t>4,68; 11,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,16; 18,75</t>
+          <t>10,89; 18,65</t>
         </is>
       </c>
     </row>
@@ -767,7 +767,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -795,32 +795,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,16; 22,8</t>
+          <t>9,86; 23,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,92; 12,3</t>
+          <t>4,01; 12,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,97; 14,5</t>
+          <t>5,9; 14,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,16; 22,8</t>
+          <t>9,86; 23,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,92; 12,3</t>
+          <t>4,01; 12,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,97; 14,5</t>
+          <t>5,9; 14,25</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>23,17%</t>
         </is>
       </c>
     </row>
@@ -875,32 +875,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,43; 26,55</t>
+          <t>14,96; 26,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,09; 17,21</t>
+          <t>7,45; 17,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,35; 24,55</t>
+          <t>17,94; 28,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,43; 26,55</t>
+          <t>14,96; 26,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,09; 17,21</t>
+          <t>7,45; 17,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,35; 24,55</t>
+          <t>17,94; 28,86</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,9%</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,33; 16,32</t>
+          <t>3,74; 16,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,28; 15,87</t>
+          <t>4,36; 16,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,22; 17,54</t>
+          <t>9,39; 17,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,33; 16,32</t>
+          <t>3,74; 16,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,28; 15,87</t>
+          <t>4,36; 16,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,22; 17,54</t>
+          <t>9,39; 17,43</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,9%</t>
         </is>
       </c>
     </row>
@@ -1035,32 +1035,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,78; 14,56</t>
+          <t>2,88; 14,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,42; 15,96</t>
+          <t>5,62; 16,48</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,76; 14,16</t>
+          <t>6,25; 14,75</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,78; 14,56</t>
+          <t>2,88; 14,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,42; 15,96</t>
+          <t>5,62; 16,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,76; 14,16</t>
+          <t>6,25; 14,75</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>34,25%</t>
         </is>
       </c>
     </row>
@@ -1115,32 +1115,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10,58; 18,55</t>
+          <t>10,4; 19,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11,0; 20,01</t>
+          <t>11,12; 19,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,19; 36,75</t>
+          <t>30,23; 39,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,58; 18,55</t>
+          <t>10,4; 19,04</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,0; 20,01</t>
+          <t>11,12; 19,5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,19; 36,75</t>
+          <t>30,23; 39,16</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,31%</t>
         </is>
       </c>
     </row>
@@ -1195,32 +1195,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>13,18; 21,81</t>
+          <t>13,35; 22,12</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>12,3; 19,9</t>
+          <t>12,37; 20,51</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,17; 15,12</t>
+          <t>8,15; 14,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13,18; 21,81</t>
+          <t>13,35; 22,12</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,3; 19,9</t>
+          <t>12,37; 20,51</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,17; 15,12</t>
+          <t>8,15; 14,97</t>
         </is>
       </c>
     </row>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>18,45%</t>
         </is>
       </c>
     </row>
@@ -1275,32 +1275,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>12,4; 16,25</t>
+          <t>12,4; 16,09</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>10,7; 14,11</t>
+          <t>10,88; 14,1</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10,23; 18,56</t>
+          <t>16,88; 20,34</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12,4; 16,25</t>
+          <t>12,4; 16,09</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>10,7; 14,11</t>
+          <t>10,88; 14,1</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,23; 18,56</t>
+          <t>16,88; 20,34</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18756</t>
+          <t>17977</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18756</t>
+          <t>17977</t>
         </is>
       </c>
     </row>
@@ -1504,32 +1504,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8613; 23687</t>
+          <t>8317; 23575</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16956; 35071</t>
+          <t>16882; 35338</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13255; 25448</t>
+          <t>13029; 25379</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8613; 23687</t>
+          <t>8317; 23575</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>16956; 35071</t>
+          <t>16882; 35338</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13255; 25448</t>
+          <t>13029; 25379</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>32497</t>
+          <t>33319</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32497</t>
+          <t>33319</t>
         </is>
       </c>
     </row>
@@ -1622,32 +1622,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18920; 41512</t>
+          <t>19260; 42358</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12490; 30189</t>
+          <t>11980; 30525</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24768; 41596</t>
+          <t>25056; 42919</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18920; 41512</t>
+          <t>19260; 42358</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12490; 30189</t>
+          <t>11980; 30525</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24768; 41596</t>
+          <t>25056; 42919</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12973</t>
+          <t>13056</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12973</t>
+          <t>13056</t>
         </is>
       </c>
     </row>
@@ -1740,32 +1740,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>15510; 34810</t>
+          <t>15054; 35242</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7122; 22356</t>
+          <t>7289; 22925</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8096; 19667</t>
+          <t>8140; 19642</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15510; 34810</t>
+          <t>15054; 35242</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7122; 22356</t>
+          <t>7289; 22925</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8096; 19667</t>
+          <t>8140; 19642</t>
         </is>
       </c>
     </row>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33465</t>
+          <t>38625</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33465</t>
+          <t>38625</t>
         </is>
       </c>
     </row>
@@ -1858,32 +1858,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>27012; 49707</t>
+          <t>28006; 49488</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14321; 34771</t>
+          <t>15054; 35750</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17046; 44732</t>
+          <t>29910; 48116</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>27012; 49707</t>
+          <t>28006; 49488</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>14321; 34771</t>
+          <t>15054; 35750</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17046; 44732</t>
+          <t>29910; 48116</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14240</t>
+          <t>15403</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14240</t>
+          <t>15403</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4497; 16956</t>
+          <t>3888; 17636</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4627; 17157</t>
+          <t>4717; 17466</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10281; 19567</t>
+          <t>11205; 20807</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4497; 16956</t>
+          <t>3888; 17636</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4627; 17157</t>
+          <t>4717; 17466</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10281; 19567</t>
+          <t>11205; 20807</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10399</t>
+          <t>11414</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10399</t>
+          <t>11414</t>
         </is>
       </c>
     </row>
@@ -2094,32 +2094,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3751; 19661</t>
+          <t>3882; 19633</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7280; 21421</t>
+          <t>7551; 22130</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6439; 15822</t>
+          <t>7209; 17006</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3751; 19661</t>
+          <t>3882; 19633</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7280; 21421</t>
+          <t>7551; 22130</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6439; 15822</t>
+          <t>7209; 17006</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>98776</t>
+          <t>112355</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98776</t>
+          <t>112355</t>
         </is>
       </c>
     </row>
@@ -2212,32 +2212,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>36666; 64291</t>
+          <t>36044; 65993</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>31403; 57133</t>
+          <t>31741; 55664</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>34885; 178201</t>
+          <t>99145; 128467</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>36666; 64291</t>
+          <t>36044; 65993</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>31403; 57133</t>
+          <t>31741; 55664</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>34885; 178201</t>
+          <t>99145; 128467</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>25016</t>
+          <t>28177</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>25016</t>
+          <t>28177</t>
         </is>
       </c>
     </row>
@@ -2330,32 +2330,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>46739; 77383</t>
+          <t>47375; 78457</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>47048; 76119</t>
+          <t>47316; 78480</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>17811; 32970</t>
+          <t>20300; 37316</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>46739; 77383</t>
+          <t>47375; 78457</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>47048; 76119</t>
+          <t>47316; 78480</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>17811; 32970</t>
+          <t>20300; 37316</t>
         </is>
       </c>
     </row>
@@ -2420,7 +2420,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>246124</t>
+          <t>270325</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>246124</t>
+          <t>270325</t>
         </is>
       </c>
     </row>
@@ -2448,32 +2448,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>202807; 265865</t>
+          <t>202798; 263179</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>180886; 238679</t>
+          <t>183949; 238421</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>161854; 293714</t>
+          <t>247339; 297997</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>202807; 265865</t>
+          <t>202798; 263179</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>180886; 238679</t>
+          <t>183949; 238421</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>161854; 293714</t>
+          <t>247339; 297997</t>
         </is>
       </c>
     </row>
